--- a/analysis.xlsx
+++ b/analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Apoorav/Projects/aider_testing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA6ABAC5-8083-A440-BFDA-7D9EE47BE490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3219B39A-620C-D24B-A1EF-C0903E1A8826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32760" yWindow="-2680" windowWidth="28020" windowHeight="17620" xr2:uid="{B5AA932F-9FB8-824D-99F9-154E6C7A2D2A}"/>
+    <workbookView xWindow="47060" yWindow="-8000" windowWidth="28020" windowHeight="17620" xr2:uid="{B5AA932F-9FB8-824D-99F9-154E6C7A2D2A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
